--- a/doctool/test/auto/scenario09/システム機能設計書_サンプル_S09_expected.xlsx
+++ b/doctool/test/auto/scenario09/システム機能設計書_サンプル_S09_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tie303229\AppData\Local\Temp\pytest-of-tie303229\pytest-21\scenario09_0\scenario09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tie303229\AppData\Local\Temp\pytest-of-tie303229\pytest-21\scenario08_0\scenario08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA0F477-3786-4A8A-96DC-D33FA1D52AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461A62F1-17FE-4B70-A160-14A0FD03589F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
@@ -1217,7 +1217,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S09</t>
+    <t>システム機能設計書_サンプル_S08</t>
   </si>
   <si>
     <t>B5</t>
@@ -3179,7 +3179,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60953CFA-4394-4A9A-B107-E54DE2F94C40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD89FD73-FA58-46D2-BAF6-19BED826A065}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3850,14 +3850,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{0214427A-61DD-4497-B880-251F02694B53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{C691E1B6-ECBF-426F-B14D-70D6C6090545}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{4FCAEF63-DC2A-422B-901A-8E67979BBD44}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{9CA08647-9FEA-421D-BAB9-31A4D62ECF29}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{C67B87D5-321E-476C-89E6-E4AE8A9AC757}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{74BEEAE5-38FF-47F1-A8F9-1DFA389A0DF2}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{75B09570-DC0B-4541-A954-22D5FF7E182E}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{E88381F7-260A-45D1-81CF-3DE7495A7791}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
